--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92701</v>
+        <v>92703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137184410</v>
       </c>
       <c r="B3" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137184389</v>
       </c>
       <c r="B4" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92703</v>
+        <v>92716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137184410</v>
       </c>
       <c r="B3" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137184389</v>
       </c>
       <c r="B4" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137184410</v>
       </c>
       <c r="B3" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137184389</v>
       </c>
       <c r="B4" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92718</v>
+        <v>92721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92721</v>
+        <v>92731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137184410</v>
       </c>
       <c r="B3" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137184389</v>
       </c>
       <c r="B4" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92731</v>
+        <v>92732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92732</v>
+        <v>92735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137184410</v>
       </c>
       <c r="B3" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137184389</v>
       </c>
       <c r="B4" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92737</v>
+        <v>92742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137184410</v>
       </c>
       <c r="B3" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137184389</v>
       </c>
       <c r="B4" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137184410</v>
       </c>
       <c r="B3" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137184389</v>
       </c>
       <c r="B4" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137184410</v>
       </c>
       <c r="B3" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137184389</v>
       </c>
       <c r="B4" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92755</v>
+        <v>92758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137184410</v>
       </c>
       <c r="B3" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137184389</v>
       </c>
       <c r="B4" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40302-2026 artfynd.xlsx
+++ b/artfynd/A 40302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137184300</v>
       </c>
       <c r="B2" t="n">
-        <v>92758</v>
+        <v>92762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137184410</v>
       </c>
       <c r="B3" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>137184389</v>
       </c>
       <c r="B4" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
